--- a/data/curated/史料录入模板.xlsx
+++ b/data/curated/史料录入模板.xlsx
@@ -667,7 +667,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>A=一手档案 B=学术著作 C=回忆录口述</t>
+          <t>A=一手档案 B=正式出版物/权威二手报道 C=回忆录/口述/展陈/待核转述</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
@@ -25061,7 +25061,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>可信度：A=一手档案（原件、档案号）；B=学术著作（有注释的正式出版物）；C=回忆录、口述、展陈说明。</t>
+          <t>可信度：A=一手档案（原件、档案号）；B=正式出版物/权威二手报道；C=回忆录、口述、展陈说明或待核转述。</t>
         </is>
       </c>
     </row>
